--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_BIOGAS_ENERGY_Α.Ε_2026-02.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_BIOGAS_ENERGY_Α.Ε_2026-02.xlsx
@@ -2844,7 +2844,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>06/03/26</t>
+          <t>09/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3196,13 +3196,13 @@
         <v>21447.1</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>81.97849600000001</v>
+        <v>1448.1520185</v>
       </c>
       <c r="F23" s="25" t="n">
         <v>5.36</v>
       </c>
       <c r="G23" s="92" t="n">
-        <v>3.82</v>
+        <v>67.52</v>
       </c>
       <c r="H23" s="93" t="n"/>
     </row>
@@ -3216,13 +3216,13 @@
         <v>14857.05</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>484.004318</v>
+        <v>526.496134</v>
       </c>
       <c r="F24" s="25" t="n">
         <v>3.71</v>
       </c>
       <c r="G24" s="92" t="n">
-        <v>32.58</v>
+        <v>35.44</v>
       </c>
       <c r="H24" s="93" t="n"/>
     </row>
@@ -3236,13 +3236,13 @@
         <v>16915.4</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>75.40792</v>
+        <v>1548.91367</v>
       </c>
       <c r="F25" s="25" t="n">
         <v>4.23</v>
       </c>
       <c r="G25" s="92" t="n">
-        <v>4.46</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="H25" s="93" t="n"/>
     </row>
@@ -3256,13 +3256,13 @@
         <v>20431.15</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>1177.6557445</v>
+        <v>1258.9850925</v>
       </c>
       <c r="F26" s="25" t="n">
         <v>5.11</v>
       </c>
       <c r="G26" s="92" t="n">
-        <v>57.64</v>
+        <v>61.62</v>
       </c>
       <c r="H26" s="93" t="n"/>
     </row>
@@ -3416,13 +3416,13 @@
         <v>16275.2</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>82.2051075</v>
+        <v>1197.1239745</v>
       </c>
       <c r="F34" s="25" t="n">
         <v>4.07</v>
       </c>
       <c r="G34" s="92" t="n">
-        <v>5.05</v>
+        <v>73.56</v>
       </c>
       <c r="H34" s="93" t="n"/>
     </row>
@@ -3436,13 +3436,13 @@
         <v>17050.4</v>
       </c>
       <c r="E35" s="25" t="n">
-        <v>1171.1040835</v>
+        <v>1248.2055505</v>
       </c>
       <c r="F35" s="25" t="n">
         <v>4.26</v>
       </c>
       <c r="G35" s="92" t="n">
-        <v>68.68000000000001</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="H35" s="93" t="n"/>
     </row>
@@ -3456,13 +3456,13 @@
         <v>21538.2</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>69.722374</v>
+        <v>1407.6900455</v>
       </c>
       <c r="F36" s="25" t="n">
         <v>5.38</v>
       </c>
       <c r="G36" s="92" t="n">
-        <v>3.24</v>
+        <v>65.36</v>
       </c>
       <c r="H36" s="93" t="n"/>
     </row>
@@ -3476,13 +3476,13 @@
         <v>17354.5</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>0</v>
+        <v>1167.435843</v>
       </c>
       <c r="F37" s="25" t="n">
         <v>4.34</v>
       </c>
       <c r="G37" s="92" t="n">
-        <v>0</v>
+        <v>67.27</v>
       </c>
       <c r="H37" s="93" t="n"/>
     </row>
@@ -3496,13 +3496,13 @@
         <v>521811.15</v>
       </c>
       <c r="E38" s="95" t="n">
-        <v>38704.03</v>
+        <v>45364.96</v>
       </c>
       <c r="F38" s="95" t="n">
         <v>130.44</v>
       </c>
       <c r="G38" s="96" t="n">
-        <v>74.17</v>
+        <v>86.94</v>
       </c>
       <c r="H38" s="93" t="n"/>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G46" s="83" t="n"/>
       <c r="H46" s="105" t="n">
-        <v>38704.03</v>
+        <v>45364.96</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C53" s="110" t="inlineStr">
         <is>
-          <t>08/03/26</t>
+          <t>11/03/26</t>
         </is>
       </c>
       <c r="D53" s="111" t="n"/>
